--- a/essais/classeur_essai.xlsx
+++ b/essais/classeur_essai.xlsx
@@ -191,7 +191,7 @@
     <t xml:space="preserve">Vaisselier vide</t>
   </si>
   <si>
-    <t xml:space="preserve">A6 : aucune capacité</t>
+    <t xml:space="preserve">I3 : aucune capacité</t>
   </si>
   <si>
     <t xml:space="preserve">Livre de cuisine</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">(Recette secrète|Recette de grand-mère)</t>
   </si>
   <si>
-    <t xml:space="preserve">A6 ; A7 : choix hors de la colonne des capacités</t>
+    <t xml:space="preserve">A7 : choix hors de la colonne des capacités ; I3</t>
   </si>
   <si>
     <t xml:space="preserve"> Fumoir </t>

--- a/essais/classeur_essai.xlsx
+++ b/essais/classeur_essai.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="327">
   <si>
     <t xml:space="preserve">Syntaxe</t>
   </si>
@@ -50,6 +50,9 @@
     <t xml:space="preserve">Infos</t>
   </si>
   <si>
+    <t xml:space="preserve">TYPE</t>
+  </si>
+  <si>
     <t xml:space="preserve">Louche d'acier</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
     <t xml:space="preserve">Liste simple</t>
   </si>
   <si>
+    <t xml:space="preserve">Arme</t>
+  </si>
+  <si>
     <t xml:space="preserve">Carnet de recettes</t>
   </si>
   <si>
@@ -74,6 +80,9 @@
     <t xml:space="preserve">Choix obligatoire</t>
   </si>
   <si>
+    <t xml:space="preserve">Equipement</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tablier</t>
   </si>
   <si>
@@ -89,6 +98,9 @@
     <t xml:space="preserve">Ensemble facultatif ; valeur composée</t>
   </si>
   <si>
+    <t xml:space="preserve">équipement</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rouleau à pâtisserie</t>
   </si>
   <si>
@@ -119,6 +131,9 @@
     <t xml:space="preserve">A1 : brulant, coup de poele</t>
   </si>
   <si>
+    <t xml:space="preserve">Équipement</t>
+  </si>
+  <si>
     <t xml:space="preserve">Poêle en fonte</t>
   </si>
   <si>
@@ -215,12 +230,234 @@
     <t xml:space="preserve">I1 : espaces de bord</t>
   </si>
   <si>
+    <t xml:space="preserve"> Consommable </t>
+  </si>
+  <si>
     <t xml:space="preserve">E3 : doublon</t>
   </si>
   <si>
     <t xml:space="preserve">E2 : ligne sans nom</t>
   </si>
   <si>
+    <t xml:space="preserve">Gestes de cuisine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dégâts(Taloche)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pas chassé, Goûter, Taloche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{degats:{force}*0,5/{force}/{force}*2}(Taloche)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloc de base ; dégâts de mains nues en expression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marmiton</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vif, Nez fin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espèce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gâte-sauce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costaud, Palais d'acier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saucier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réduction, Flambage, Dressage minute, (Solo du chef | Brigade), (Maîtrise du lourd | Maîtrise de l'agile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archétype : style et maîtrise au choix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archétype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pâtissier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feuilletage, Glaçage, Coup de chalumeau, (Brigade | Minutie), (Maîtrise de l'agile | Maîtrise du précis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archetype</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constellation du Chaudron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouillonnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constellation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constellation de la Cuillère</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cuillère d'argent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constellation du Sablier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constellation sans capacité ; I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand Four</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fournaise, (Braise | Cendre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primordial : une capacité à trois puissances, un choix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primordial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Givre éternel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primordial sans capacité ; I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rouleau de fonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme, Lourde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frappe, Choc sourd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{degats:8/11/13}, {qualite:X}, {portee:0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme lourde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatule souple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme, Agile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frappe, Moulinet farineux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{degats:5/10/15}, {qualite:X}, {portee:0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme agile ; Moulinet farineux, comme la louche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couteau d'office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme, Précise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frappe, Émincer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{degats:3/8/20}, {qualite:X}, {portee:1}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme précise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tablier de cuir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armure, Agile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{armure:30/0/0/0/0/0}, {qualite:X}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armure du torse ; I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plastron de fonte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armure, Lourde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{armure:40/0/0/0/0/0}, {qualite:X}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armure du torse, comme le tablier de cuir ; I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guêtres de toile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armure, Précise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{armure:0/10/10/0/0/0}, {qualite:X}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armure des deux jambes ; I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maniques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{armure:0/0/0/15/15/0}, {qualite:X}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armure des deux bras ; I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toque renforcée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{armure:0/0/0/0/0/5}, {qualite:X}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armure de la tête ; I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couvercle de marmite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se couvrir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{defense:8}, {qualite:X}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouclier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouillon revigorant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boire le bouillon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consommable</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paramètres reçus</t>
   </si>
   <si>
@@ -285,6 +522,78 @@
   </si>
   <si>
     <t xml:space="preserve">E2 : ligne sans nom.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une seule arme en main à la fois.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lourde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme : Force et Précision. Armure : Force et Sens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme : Agilité et Force. Armure : Agilité et Créativité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Précise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme : Précision et Agilité. Armure : Précision et Empathie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{armure}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octroie [A] points au torse, [B] à la jambe gauche, [C] à la jambe droite, [D] au bras gauche, [E] au bras droit et [F] à la tête. Deux pièces sur une même zone ne s'additionnent pas : la plus élevée l'emporte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dégâts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{degats}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inflige [A] sur une réussite, [B] sur deux, [C] sur trois.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{qualite}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multipliez {degats}, {defense} et {armure} de ce bloc par [1/3 + {qualite}/3].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{portee}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atteint {portee} cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Défense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{defense}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le bouclier encaisse jusqu'à {defense} points.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Style de combat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ne s'acquiert qu'à la création.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maîtrise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octroyée par l'archétype.</t>
   </si>
   <si>
     <t xml:space="preserve">puissance</t>
@@ -456,6 +765,189 @@
   </si>
   <si>
     <t xml:space="preserve">E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pas chassé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se déplace de [N] cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Goûter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fait un jet de caractéristique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taloche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une taloche qui inflige [N*{degats}].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base : mains nues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajoutez [N] aux jets d'agilité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nez fin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retournez un dé devant un plat douteux.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costaud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajoutez [N] aux jets de force.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palais d'acier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retournez un dé face à un poison.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réduction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retire [N] points d'armure par réussite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flambage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplie les dégâts par [1+N].</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dressage minute</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sert un allié avant son tour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feuilletage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pare [N] coups par tour.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glaçage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fige la cible pendant [N] tours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coup de chalumeau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gagne un point de lien.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solo du chef</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seul sur sa case : [N] avantages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brigade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avec un allié sur sa case : [N] avantages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minutie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contre la même cible : [N] avantages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maîtrise du lourd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les [N] premières capacités d'un objet Lourde, sans désavantage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maîtrise de l'agile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les [N] premières capacités d'un objet Agile, sans désavantage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maîtrise du précis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les [N] premières capacités d'un objet Précise, sans désavantage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2*N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fait bouillir [N] marmites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une fois par jour, relance un dé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fournaise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réchauffe la case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primordial : trois puissances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portée[1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brûle trois adversaires à {portee} case.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portée[2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aveugle une cible à {portee} cases.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Braise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rallume [N] feux.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cendre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disparaît dans la fumée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frappe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une attaque qui inflige {degats}.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choc sourd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La cible perd autant d'attaque que vos réussites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Émincer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une réussite de plus si vous en avez une.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reportez les dommages sur les {defense} points du couvercle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regagnez 5 points de résistance.</t>
   </si>
   <si>
     <t xml:space="preserve">Forme</t>
@@ -628,235 +1120,605 @@
       <c r="E1" t="s">
         <v>11</v>
       </c>
+      <c r="F1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>24</v>
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>33</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>38</v>
+      </c>
+      <c r="F6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="F9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E10" t="s">
-        <v>50</v>
+        <v>55</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>59</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>62</v>
+        <v>67</v>
+      </c>
+      <c r="F14" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>71</v>
+      </c>
+      <c r="F15" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E16" t="s">
-        <v>67</v>
+        <v>73</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>74</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>93</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E25" t="s">
+        <v>99</v>
+      </c>
+      <c r="F25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" t="s">
+        <v>105</v>
+      </c>
+      <c r="F27" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E28" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" t="s">
+        <v>115</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" t="s">
+        <v>124</v>
+      </c>
+      <c r="F31" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B32" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" t="s">
+        <v>132</v>
+      </c>
+      <c r="E33" t="s">
+        <v>133</v>
+      </c>
+      <c r="F33" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" t="s">
+        <v>122</v>
+      </c>
+      <c r="D34" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" t="s">
+        <v>136</v>
+      </c>
+      <c r="F34" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" t="s">
+        <v>139</v>
+      </c>
+      <c r="F35" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" t="s">
+        <v>143</v>
+      </c>
+      <c r="E36" t="s">
+        <v>144</v>
+      </c>
+      <c r="F36" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -871,99 +1733,202 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>69</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>70</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C2" t="s">
-        <x:v>71</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
-        <x:v>72</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>73</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>74</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
-        <x:v>75</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>76</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C4" t="s">
-        <x:v>77</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>78</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>79</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>80</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>81</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="s">
-        <x:v>82</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>83</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="s">
-        <x:v>84</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>85</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="s">
-        <x:v>86</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>87</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>88</x:v>
+        <x:v>167</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="B11" t="s">
-        <x:v>89</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>90</x:v>
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C12" t="s">
+        <x:v>170</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C13" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="C14" t="s">
+        <x:v>174</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="s">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="C15" t="s">
+        <x:v>176</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B16" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C16" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B17" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C17" t="s">
+        <x:v>181</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B18" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C18" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B19" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C19" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B20" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C20" t="s">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C21" t="s">
+        <x:v>191</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="C22" t="s">
+        <x:v>193</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -978,27 +1943,27 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="C1" t="s">
-        <v>92</v>
+        <v>195</v>
       </c>
       <c r="D1" t="s">
-        <v>93</v>
+        <v>196</v>
       </c>
       <c r="E1" t="s">
-        <v>94</v>
+        <v>197</v>
       </c>
       <c r="F1" t="s">
-        <v>95</v>
+        <v>198</v>
       </c>
       <c r="G1" t="s">
-        <v>96</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1007,58 +1972,58 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>97</v>
+        <v>200</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>201</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>101</v>
+        <v>204</v>
       </c>
       <c r="G3" t="s">
-        <v>102</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>208</v>
       </c>
       <c r="F4" t="s">
-        <v>106</v>
+        <v>209</v>
       </c>
       <c r="G4" t="s">
-        <v>107</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1067,18 +2032,18 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="F5" t="s">
-        <v>109</v>
+        <v>212</v>
       </c>
       <c r="G5" t="s">
-        <v>110</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1087,15 +2052,15 @@
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="F6" t="s">
-        <v>109</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -1107,15 +2072,15 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="F7" t="s">
-        <v>109</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -1124,82 +2089,82 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>72</v>
+        <v>151</v>
       </c>
       <c r="F8" t="s">
-        <v>111</v>
+        <v>214</v>
       </c>
       <c r="G8" t="s">
-        <v>112</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>216</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>114</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>218</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>116</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>220</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>118</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>222</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>120</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>121</v>
+        <v>224</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>202</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>225</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="F13" t="s">
-        <v>123</v>
+        <v>226</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>227</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1208,83 +2173,83 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>125</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>229</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>127</v>
+        <v>230</v>
       </c>
       <c r="F15" t="s">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="G15" t="s">
-        <v>129</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>131</v>
+        <v>234</v>
       </c>
       <c r="G16" t="s">
-        <v>132</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>133</v>
+        <v>236</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>134</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>239</v>
       </c>
       <c r="F18" t="s">
-        <v>137</v>
+        <v>240</v>
       </c>
       <c r="G18" t="s">
-        <v>138</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>242</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>140</v>
+        <v>243</v>
       </c>
       <c r="G19" t="s">
-        <v>141</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20">
@@ -1295,10 +2260,537 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
+        <v>245</v>
+      </c>
+      <c r="G20" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B21" t="s">
+        <v>202</v>
+      </c>
+      <c r="C21" t="s">
+        <v>225</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>249</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>250</v>
+      </c>
+      <c r="G22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>251</v>
+      </c>
+      <c r="B23" t="s">
+        <v>202</v>
+      </c>
+      <c r="F23" t="s">
+        <v>252</v>
+      </c>
+      <c r="G23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>254</v>
+      </c>
+      <c r="B24" t="s">
+        <v>202</v>
+      </c>
+      <c r="F24" t="s">
+        <v>255</v>
+      </c>
+      <c r="G24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>256</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="F25" t="s">
+        <v>257</v>
+      </c>
+      <c r="G25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>258</v>
+      </c>
+      <c r="B26" t="s">
+        <v>202</v>
+      </c>
+      <c r="F26" t="s">
+        <v>259</v>
+      </c>
+      <c r="G26" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>260</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>261</v>
+      </c>
+      <c r="G27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" t="s">
+        <v>202</v>
+      </c>
+      <c r="F28" t="s">
+        <v>263</v>
+      </c>
+      <c r="G28" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>264</v>
+      </c>
+      <c r="B29" t="s">
+        <v>202</v>
+      </c>
+      <c r="C29" t="s">
+        <v>203</v>
+      </c>
+      <c r="F29" t="s">
+        <v>265</v>
+      </c>
+      <c r="G29" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>266</v>
+      </c>
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="F30" t="s">
+        <v>267</v>
+      </c>
+      <c r="G30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>268</v>
+      </c>
+      <c r="B31" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" t="s">
+        <v>269</v>
+      </c>
+      <c r="G31" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>270</v>
+      </c>
+      <c r="B32" t="s">
+        <v>202</v>
+      </c>
+      <c r="C32" t="s">
+        <v>203</v>
+      </c>
+      <c r="F32" t="s">
+        <v>271</v>
+      </c>
+      <c r="G32" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>272</v>
+      </c>
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>273</v>
+      </c>
+      <c r="G33" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>274</v>
+      </c>
+      <c r="B34" t="s">
+        <v>202</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34" t="s">
+        <v>190</v>
+      </c>
+      <c r="F34" t="s">
+        <v>275</v>
+      </c>
+      <c r="G34" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>276</v>
+      </c>
+      <c r="B35" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35" t="s">
+        <v>190</v>
+      </c>
+      <c r="F35" t="s">
+        <v>277</v>
+      </c>
+      <c r="G35" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>278</v>
+      </c>
+      <c r="B36" t="s">
+        <v>202</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
+        <v>190</v>
+      </c>
+      <c r="F36" t="s">
+        <v>279</v>
+      </c>
+      <c r="G36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>280</v>
+      </c>
+      <c r="B37" t="s">
+        <v>202</v>
+      </c>
+      <c r="E37" t="s">
+        <v>192</v>
+      </c>
+      <c r="F37" t="s">
+        <v>281</v>
+      </c>
+      <c r="G37" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>282</v>
+      </c>
+      <c r="B38" t="s">
+        <v>202</v>
+      </c>
+      <c r="E38" t="s">
+        <v>192</v>
+      </c>
+      <c r="F38" t="s">
+        <v>283</v>
+      </c>
+      <c r="G38" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>284</v>
+      </c>
+      <c r="B39" t="s">
+        <v>202</v>
+      </c>
+      <c r="E39" t="s">
+        <v>192</v>
+      </c>
+      <c r="F39" t="s">
+        <v>285</v>
+      </c>
+      <c r="G39" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" t="s">
+        <v>202</v>
+      </c>
+      <c r="C40" t="s">
+        <v>286</v>
+      </c>
+      <c r="F40" t="s">
+        <v>287</v>
+      </c>
+      <c r="G40" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>97</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="F41" t="s">
+        <v>288</v>
+      </c>
+      <c r="G41" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>289</v>
+      </c>
+      <c r="B42">
+        <v>1</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="F42" t="s">
+        <v>290</v>
+      </c>
+      <c r="G42" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>289</v>
+      </c>
+      <c r="B43">
+        <v>2</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>292</v>
+      </c>
+      <c r="F43" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>289</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
+      </c>
+      <c r="C44">
+        <v>7</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
+        <v>294</v>
+      </c>
+      <c r="F44" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>296</v>
+      </c>
+      <c r="B45" t="s">
+        <v>202</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>297</v>
+      </c>
+      <c r="G45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>298</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>299</v>
+      </c>
+      <c r="G46" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>300</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="F47" t="s">
+        <v>301</v>
+      </c>
+      <c r="G47" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>302</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="F48" t="s">
+        <v>303</v>
+      </c>
+      <c r="G48" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>304</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="F49" t="s">
+        <v>305</v>
+      </c>
+      <c r="G49" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
         <v>142</v>
       </c>
-      <c r="G20" t="s">
-        <v>143</v>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="F50" t="s">
+        <v>306</v>
+      </c>
+      <c r="G50" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>146</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="F51" t="s">
+        <v>307</v>
+      </c>
+      <c r="G51" t="s">
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1310,23 +2802,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>144</v>
+        <v>308</v>
       </c>
       <c r="B1" t="s">
-        <v>145</v>
+        <v>309</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>310</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>312</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -1336,39 +2828,39 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>315</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>317</v>
       </c>
       <c r="B6" t="s">
-        <v>154</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>155</v>
+        <v>319</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>321</v>
       </c>
       <c r="B8" t="str">
         <f>CONCATENATE("for","mule")</f>
@@ -1377,7 +2869,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>322</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -1388,7 +2880,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>159</v>
+        <v>323</v>
       </c>
       <c r="B10" t="e">
         <v>#N/A</v>
@@ -1396,7 +2888,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>324</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -1416,10 +2908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>161</v>
+        <v>325</v>
       </c>
       <c r="AB13" t="s">
-        <v>162</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>

--- a/essais/classeur_essai.xlsx
+++ b/essais/classeur_essai.xlsx
@@ -188,10 +188,10 @@
     <t xml:space="preserve">Coup de louche, Jet de sel</t>
   </si>
   <si>
-    <t xml:space="preserve">{distance:0}, {distance:1}(Jet de sel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E7 : Jet de sel reçoit deux distances</t>
+    <t xml:space="preserve">{distance:0}, {distance:1}(Jet de sel), {distance:2}(Jet de sel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E7 : Jet de sel visé deux fois (la distance sans cible est admise)</t>
   </si>
   <si>
     <t xml:space="preserve">Sablier de cuisine</t>

--- a/essais/classeur_essai.xlsx
+++ b/essais/classeur_essai.xlsx
@@ -7,12 +7,13 @@
     <sheet name="Eléments" sheetId="3" r:id="rId3"/>
     <sheet name="Capacites" sheetId="4" r:id="rId4"/>
     <sheet name="Formes de cellules" sheetId="5" r:id="rId5"/>
+    <sheet name="Adversaires" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="368">
   <si>
     <t xml:space="preserve">Syntaxe</t>
   </si>
@@ -456,6 +457,30 @@
   </si>
   <si>
     <t xml:space="preserve">Consommable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinces de homard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{degats:4/8/12}, {portee:0}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme naturelle : hors du créateur de personnage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arme naturelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carapace épaisse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{armure:30}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armure naturelle globale : une seule valeur ; I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">armure naturelle</t>
   </si>
   <si>
     <t xml:space="preserve">Paramètres reçus</t>
@@ -1022,6 +1047,110 @@
   </si>
   <si>
     <t xml:space="preserve">colonne AB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nombre  d'actions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">souffle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Attaque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capacites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torse(2),
+Jambe gauche(12),
+Jambre droite(14),
+Bras gauche(16),
+Bras droit(18),
+Tête(20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type ; A11 : « Jambre droite » se lit « jambe droite »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rôtisseur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spatule souple, Armure agile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">//, Maitrise de l'agile[1]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type ; « // » reprend la liste héritée ; un pack d'armure ; A1 : Maitrise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marmiton de corvée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commis/Rôtisseur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deux types, rien en propre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chef de partie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commis/Rôtisseur[1,4]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">//, Maîtrise de l'agile[3], Pas chassé[2]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiplicateur décimal ; deux rangs en remplacent d'autres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plongeur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commis / Rôtisseur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aucun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« aucun » : ni souffle, ni équipement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homard furieux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corps(2), Pince gauche(12), Pince droite(15), Tête(18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carapace épaisse, Toque renforcée[3], Pinces de homard, Couteau d'office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sans type ; armure naturelle globale plus une pièce ; deux armes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mouette chapardeuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corps(2), Aile gauche(14), Aile  droite(17), Tête(20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frappe, Nez fin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A15 : Frappe, sans arme pour ses dégâts</t>
   </si>
 </sst>
 </file>
@@ -1721,6 +1850,43 @@
         <v>147</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
+        <v>108</v>
+      </c>
+      <c r="D38" t="s">
+        <v>149</v>
+      </c>
+      <c r="E38" t="s">
+        <v>150</v>
+      </c>
+      <c r="F38" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" t="s">
+        <v>154</v>
+      </c>
+      <c r="F39" t="s">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1733,10 +1899,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>148</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>149</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -1744,37 +1910,37 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C2" t="s">
-        <x:v>150</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
-        <x:v>151</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>152</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>153</x:v>
+        <x:v>161</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
-        <x:v>154</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>155</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C4" t="s">
-        <x:v>156</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>157</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>158</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1782,34 +1948,34 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>159</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>160</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="s">
-        <x:v>161</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>162</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="s">
-        <x:v>163</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>164</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="s">
-        <x:v>165</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>166</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1817,15 +1983,15 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>167</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="B11" t="s">
-        <x:v>168</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>169</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1833,31 +1999,31 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>170</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="s">
-        <x:v>171</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>172</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="s">
-        <x:v>173</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>174</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="s">
-        <x:v>175</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>176</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1865,21 +2031,21 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>177</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>178</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="s">
-        <x:v>179</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>180</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>181</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1887,48 +2053,48 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>182</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>183</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="s">
-        <x:v>184</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>185</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>186</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="s">
-        <x:v>187</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>188</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>189</x:v>
+        <x:v>197</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="s">
-        <x:v>190</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>191</x:v>
+        <x:v>199</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="s">
-        <x:v>192</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>193</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1943,22 +2109,22 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="D1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="E1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2">
@@ -1975,7 +2141,7 @@
         <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="G2" t="s">
         <v>17</v>
@@ -1983,47 +2149,47 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="B3" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G3" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E4" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="F4" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -2032,18 +2198,18 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F5" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G5" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2052,15 +2218,15 @@
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F6" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -2072,15 +2238,15 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F7" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -2089,74 +2255,74 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F8" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G8" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B13" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C13" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E13" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F13" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="G13" t="s">
         <v>71</v>
@@ -2164,7 +2330,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2176,80 +2342,80 @@
         <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F15" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="G15" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G16" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F18" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="G18" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="G19" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20">
@@ -2260,27 +2426,27 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G20" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B21" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C21" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="G21" t="s">
         <v>80</v>
@@ -2288,13 +2454,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="G22" t="s">
         <v>80</v>
@@ -2302,27 +2468,27 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F23" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="G23" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B24" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F24" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="G24" t="s">
         <v>83</v>
@@ -2330,7 +2496,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2339,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="G25" t="s">
         <v>83</v>
@@ -2347,13 +2513,13 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F26" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="G26" t="s">
         <v>83</v>
@@ -2361,7 +2527,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2370,7 +2536,7 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="G27" t="s">
         <v>83</v>
@@ -2378,13 +2544,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F28" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="G28" t="s">
         <v>89</v>
@@ -2392,16 +2558,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C29" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F29" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="G29" t="s">
         <v>89</v>
@@ -2409,13 +2575,13 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="G30" t="s">
         <v>89</v>
@@ -2423,13 +2589,13 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F31" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="G31" t="s">
         <v>89</v>
@@ -2437,16 +2603,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B32" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C32" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F32" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2454,7 +2620,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2463,7 +2629,7 @@
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2471,10 +2637,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2483,21 +2649,21 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F34" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="G34" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2506,21 +2672,21 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F35" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G35" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2529,64 +2695,64 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F36" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="G36" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="B37" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E37" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F37" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="G37" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E38" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F38" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="G38" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E39" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F39" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="G39" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40">
@@ -2594,13 +2760,13 @@
         <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="C40" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="F40" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="G40" t="s">
         <v>95</v>
@@ -2614,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="G41" t="s">
         <v>95</v>
@@ -2622,7 +2788,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -2634,15 +2800,15 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="G42" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -2654,15 +2820,15 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="F43" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -2674,24 +2840,24 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F44" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B45" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="G45" t="s">
         <v>103</v>
@@ -2699,7 +2865,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2711,7 +2877,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="G46" t="s">
         <v>103</v>
@@ -2719,13 +2885,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="G47" t="s">
         <v>18</v>
@@ -2733,7 +2899,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2742,7 +2908,7 @@
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="G48" t="s">
         <v>18</v>
@@ -2750,7 +2916,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2759,7 +2925,7 @@
         <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="G49" t="s">
         <v>18</v>
@@ -2773,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="G50" t="s">
         <v>144</v>
@@ -2787,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="G51" t="s">
         <v>147</v>
@@ -2802,23 +2968,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="B1" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="B2" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2828,39 +2994,39 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B5" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="B6" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B7" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B8" t="str">
         <f>CONCATENATE("for","mule")</f>
@@ -2869,7 +3035,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -2880,7 +3046,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B10" t="e">
         <v>#N/A</v>
@@ -2888,7 +3054,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -2908,10 +3074,195 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="AB13" t="s">
-        <v>326</v>
+        <v>334</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D1" t="s">
+        <v>336</v>
+      </c>
+      <c r="E1" t="s">
+        <v>337</v>
+      </c>
+      <c r="F1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G1" t="s">
+        <v>339</v>
+      </c>
+      <c r="H1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" t="s">
+        <v>340</v>
+      </c>
+      <c r="J1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>3</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+      <c r="I2" t="s">
+        <v>255</v>
+      </c>
+      <c r="J2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E3">
+        <v>5</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>5</v>
+      </c>
+      <c r="H3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I3" t="s">
+        <v>347</v>
+      </c>
+      <c r="J3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B4" t="s">
+        <v>350</v>
+      </c>
+      <c r="J4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>352</v>
+      </c>
+      <c r="B5" t="s">
+        <v>353</v>
+      </c>
+      <c r="I5" t="s">
+        <v>354</v>
+      </c>
+      <c r="J5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>356</v>
+      </c>
+      <c r="B6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E6" t="s">
+        <v>358</v>
+      </c>
+      <c r="H6" t="s">
+        <v>358</v>
+      </c>
+      <c r="J6" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>362</v>
+      </c>
+      <c r="J7" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C8" t="s">
+        <v>365</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>3</v>
+      </c>
+      <c r="I8" t="s">
+        <v>366</v>
+      </c>
+      <c r="J8" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/essais/classeur_essai.xlsx
+++ b/essais/classeur_essai.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="379">
   <si>
     <t xml:space="preserve">Syntaxe</t>
   </si>
@@ -246,7 +246,7 @@
     <t xml:space="preserve">Dégâts(Taloche)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pas chassé, Goûter, Taloche</t>
+    <t xml:space="preserve">Pas chassé, Goûter, Taloche, Pas de côté, Guetter</t>
   </si>
   <si>
     <t xml:space="preserve">{degats:{force}*0,5/{force}/{force}*2}(Taloche)</t>
@@ -619,6 +619,18 @@
   </si>
   <si>
     <t xml:space="preserve">Octroyée par l'archétype.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se joue pendant le tour adverse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Passif</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agit sans action.</t>
   </si>
   <si>
     <t xml:space="preserve">puissance</t>
@@ -876,6 +888,9 @@
     <t xml:space="preserve">Solo du chef</t>
   </si>
   <si>
+    <t xml:space="preserve">Style de combat, Passif</t>
+  </si>
+  <si>
     <t xml:space="preserve">Seul sur sa case : [N] avantages.</t>
   </si>
   <si>
@@ -894,6 +909,9 @@
     <t xml:space="preserve">Maîtrise du lourd</t>
   </si>
   <si>
+    <t xml:space="preserve">Maîtrise, Passif</t>
+  </si>
+  <si>
     <t xml:space="preserve">Les [N] premières capacités d'un objet Lourde, sans désavantage.</t>
   </si>
   <si>
@@ -973,6 +991,21 @@
   </si>
   <si>
     <t xml:space="preserve">Regagnez 5 points de résistance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pas de côté</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annulez [X] dégâts reçus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base : intervention, coût X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guetter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Après un déplacement, ou pour finir son tour : une de vos capacités se joue en intervention jusqu'au prochain tour de votre camp.</t>
   </si>
   <si>
     <t xml:space="preserve">Forme</t>
@@ -2097,6 +2130,22 @@
         <x:v>201</x:v>
       </x:c>
     </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="C23" t="s">
+        <x:v>203</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C24" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -2109,22 +2158,22 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="E1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2">
@@ -2141,7 +2190,7 @@
         <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="G2" t="s">
         <v>17</v>
@@ -2149,47 +2198,47 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -2201,15 +2250,15 @@
         <v>159</v>
       </c>
       <c r="F5" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G5" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2221,12 +2270,12 @@
         <v>159</v>
       </c>
       <c r="F6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -2241,12 +2290,12 @@
         <v>159</v>
       </c>
       <c r="F7" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -2258,71 +2307,71 @@
         <v>159</v>
       </c>
       <c r="F8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G8" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B13" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C13" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E13" t="s">
         <v>165</v>
       </c>
       <c r="F13" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="G13" t="s">
         <v>71</v>
@@ -2330,7 +2379,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2342,80 +2391,80 @@
         <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F15" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="G15" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G16" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="F18" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G18" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="G19" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20">
@@ -2426,27 +2475,27 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="G20" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B21" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C21" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G21" t="s">
         <v>80</v>
@@ -2454,13 +2503,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="G22" t="s">
         <v>80</v>
@@ -2468,27 +2517,30 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B23" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F23" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G23" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B24" t="s">
-        <v>210</v>
+        <v>214</v>
+      </c>
+      <c r="E24" t="s">
+        <v>204</v>
       </c>
       <c r="F24" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="G24" t="s">
         <v>83</v>
@@ -2496,7 +2548,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2504,8 +2556,11 @@
       <c r="C25">
         <v>1</v>
       </c>
+      <c r="E25" t="s">
+        <v>204</v>
+      </c>
       <c r="F25" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G25" t="s">
         <v>83</v>
@@ -2513,13 +2568,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B26" t="s">
-        <v>210</v>
+        <v>214</v>
+      </c>
+      <c r="E26" t="s">
+        <v>204</v>
       </c>
       <c r="F26" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G26" t="s">
         <v>83</v>
@@ -2527,7 +2585,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2535,8 +2593,11 @@
       <c r="C27">
         <v>1</v>
       </c>
+      <c r="E27" t="s">
+        <v>204</v>
+      </c>
       <c r="F27" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="G27" t="s">
         <v>83</v>
@@ -2544,13 +2605,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B28" t="s">
-        <v>210</v>
+        <v>214</v>
+      </c>
+      <c r="E28" t="s">
+        <v>204</v>
       </c>
       <c r="F28" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G28" t="s">
         <v>89</v>
@@ -2558,16 +2622,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B29" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C29" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F29" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G29" t="s">
         <v>89</v>
@@ -2575,13 +2639,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
+      <c r="E30" t="s">
+        <v>202</v>
+      </c>
       <c r="F30" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="G30" t="s">
         <v>89</v>
@@ -2589,13 +2656,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s">
-        <v>210</v>
+        <v>214</v>
+      </c>
+      <c r="E31" t="s">
+        <v>204</v>
       </c>
       <c r="F31" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="G31" t="s">
         <v>89</v>
@@ -2603,16 +2673,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C32" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="F32" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2620,7 +2690,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2628,8 +2698,11 @@
       <c r="C33">
         <v>10</v>
       </c>
+      <c r="E33" t="s">
+        <v>202</v>
+      </c>
       <c r="F33" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2637,10 +2710,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2649,10 +2722,10 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>198</v>
+        <v>287</v>
       </c>
       <c r="F34" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="G34" t="s">
         <v>198</v>
@@ -2660,10 +2733,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2672,10 +2745,10 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>198</v>
+        <v>287</v>
       </c>
       <c r="F35" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="G35" t="s">
         <v>198</v>
@@ -2683,10 +2756,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2695,10 +2768,10 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>198</v>
+        <v>287</v>
       </c>
       <c r="F36" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G36" t="s">
         <v>198</v>
@@ -2706,16 +2779,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="B37" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E37" t="s">
-        <v>200</v>
+        <v>294</v>
       </c>
       <c r="F37" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="G37" t="s">
         <v>200</v>
@@ -2723,16 +2796,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B38" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E38" t="s">
-        <v>200</v>
+        <v>294</v>
       </c>
       <c r="F38" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="G38" t="s">
         <v>200</v>
@@ -2740,16 +2813,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E39" t="s">
-        <v>200</v>
+        <v>294</v>
       </c>
       <c r="F39" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G39" t="s">
         <v>200</v>
@@ -2760,13 +2833,13 @@
         <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C40" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F40" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="G40" t="s">
         <v>95</v>
@@ -2780,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="G41" t="s">
         <v>95</v>
@@ -2788,7 +2861,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -2800,15 +2873,15 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G42" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -2820,15 +2893,15 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F43" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -2840,24 +2913,24 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="F44" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B45" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="G45" t="s">
         <v>103</v>
@@ -2865,7 +2938,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2877,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="G46" t="s">
         <v>103</v>
@@ -2885,13 +2958,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="G47" t="s">
         <v>18</v>
@@ -2899,7 +2972,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2908,7 +2981,7 @@
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="G48" t="s">
         <v>18</v>
@@ -2916,7 +2989,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -2925,7 +2998,7 @@
         <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="G49" t="s">
         <v>18</v>
@@ -2939,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="G50" t="s">
         <v>144</v>
@@ -2953,10 +3026,44 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="G51" t="s">
         <v>147</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>322</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52" t="s">
+        <v>219</v>
+      </c>
+      <c r="E52" t="s">
+        <v>202</v>
+      </c>
+      <c r="F52" t="s">
+        <v>323</v>
+      </c>
+      <c r="G52" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>325</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="F53" t="s">
+        <v>326</v>
+      </c>
+      <c r="G53" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2968,23 +3075,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B1" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B2" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2994,39 +3101,39 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B4" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B5" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B6" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B7" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B8" t="str">
         <f>CONCATENATE("for","mule")</f>
@@ -3035,7 +3142,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -3046,7 +3153,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B10" t="e">
         <v>#N/A</v>
@@ -3054,7 +3161,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -3074,10 +3181,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="AB13" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -3095,25 +3202,25 @@
         <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="D1" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="E1" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="F1" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="G1" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="H1" t="s">
         <v>39</v>
       </c>
       <c r="I1" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="J1" t="s">
         <v>11</v>
@@ -3121,13 +3228,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B2" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="C2" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -3142,18 +3249,18 @@
         <v>4</v>
       </c>
       <c r="I2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="J2" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="B3" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -3165,63 +3272,63 @@
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="I3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="J3" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B4" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="J4" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B5" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="I5" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="J5" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="B6" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="E6" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="H6" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="J6" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="C7" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -3236,18 +3343,18 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="J7" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="C8" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -3259,10 +3366,10 @@
         <v>3</v>
       </c>
       <c r="I8" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="J8" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
   </sheetData>

--- a/essais/classeur_essai.xlsx
+++ b/essais/classeur_essai.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="380">
   <si>
     <t xml:space="preserve">Syntaxe</t>
   </si>
@@ -1082,7 +1082,10 @@
     <t xml:space="preserve">colonne AB</t>
   </si>
   <si>
-    <t xml:space="preserve">Localisation</t>
+    <t xml:space="preserve">CLASSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Localisations</t>
   </si>
   <si>
     <t xml:space="preserve">Nombre  d'actions</t>
@@ -1100,7 +1103,7 @@
     <t xml:space="preserve">Capacites</t>
   </si>
   <si>
-    <t xml:space="preserve">Type</t>
+    <t xml:space="preserve">Classe</t>
   </si>
   <si>
     <t xml:space="preserve">Commis</t>
@@ -1114,7 +1117,7 @@
 Tête(20)</t>
   </si>
   <si>
-    <t xml:space="preserve">Type ; A11 : « Jambre droite » se lit « jambe droite »</t>
+    <t xml:space="preserve">Classe ; A11 : « Jambre droite » se lit « jambe droite »</t>
   </si>
   <si>
     <t xml:space="preserve">Rôtisseur</t>
@@ -1126,7 +1129,7 @@
     <t xml:space="preserve">//, Maitrise de l'agile[1]</t>
   </si>
   <si>
-    <t xml:space="preserve">Type ; « // » reprend la liste héritée ; un pack d'armure ; A1 : Maitrise</t>
+    <t xml:space="preserve">Classe ; « // » reprend la liste héritée ; un pack d'armure ; A1 : Maitrise</t>
   </si>
   <si>
     <t xml:space="preserve">Marmiton de corvée</t>
@@ -3199,28 +3202,28 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>346</v>
       </c>
       <c r="C1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1" t="s">
         <v>39</v>
       </c>
       <c r="I1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J1" t="s">
         <v>11</v>
@@ -3228,13 +3231,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -3252,15 +3255,15 @@
         <v>259</v>
       </c>
       <c r="J2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -3272,63 +3275,63 @@
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I3" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="I5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -3343,18 +3346,18 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C8" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -3366,10 +3369,10 @@
         <v>3</v>
       </c>
       <c r="I8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>

--- a/essais/classeur_essai.xlsx
+++ b/essais/classeur_essai.xlsx
@@ -498,7 +498,7 @@
     <t xml:space="preserve">{chaleur}</t>
   </si>
   <si>
-    <t xml:space="preserve">Brûle de {chaleur} points.</t>
+    <t xml:space="preserve">Brûle de {chaleur} point(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Distance</t>
@@ -519,7 +519,7 @@
     <t xml:space="preserve">{epaisseur}</t>
   </si>
   <si>
-    <t xml:space="preserve">Protège de {epaisseur} points.</t>
+    <t xml:space="preserve">Protège de {epaisseur} point(s).</t>
   </si>
   <si>
     <t xml:space="preserve"> Fumant </t>
@@ -573,7 +573,7 @@
     <t xml:space="preserve">{armure}</t>
   </si>
   <si>
-    <t xml:space="preserve">Octroie [A] points au torse, [B] à la jambe gauche, [C] à la jambe droite, [D] au bras gauche, [E] au bras droit et [F] à la tête. Deux pièces sur une même zone ne s'additionnent pas : la plus élevée l'emporte.</t>
+    <t xml:space="preserve">Octroie [A] point(s) au torse, [B] à la jambe gauche, [C] à la jambe droite, [D] au bras gauche, [E] au bras droit et [F] à la tête. Deux pièces sur une même zone ne s'additionnent pas : la plus élevée l'emporte.</t>
   </si>
   <si>
     <t xml:space="preserve">Dégâts</t>
@@ -597,7 +597,7 @@
     <t xml:space="preserve">{portee}</t>
   </si>
   <si>
-    <t xml:space="preserve">Atteint {portee} cases.</t>
+    <t xml:space="preserve">Atteint {portee} case(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Défense</t>
@@ -606,7 +606,7 @@
     <t xml:space="preserve">{defense}</t>
   </si>
   <si>
-    <t xml:space="preserve">Le bouclier encaisse jusqu'à {defense} points.</t>
+    <t xml:space="preserve">Le bouclier encaisse jusqu'à {defense} point(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Style de combat</t>
@@ -651,7 +651,7 @@
     <t xml:space="preserve">origine</t>
   </si>
   <si>
-    <t xml:space="preserve">Frappe pour {chaleur} points.</t>
+    <t xml:space="preserve">Frappe pour {chaleur} point(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Moulinet farineux</t>
@@ -699,7 +699,7 @@
     <t xml:space="preserve">Sauce piquante</t>
   </si>
   <si>
-    <t xml:space="preserve">[N*{chaleur}] points.</t>
+    <t xml:space="preserve">[N*{chaleur}] point(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Trois puissances</t>
@@ -741,7 +741,7 @@
     <t xml:space="preserve">N-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Mijote [N] tours.</t>
+    <t xml:space="preserve">Mijote [N] tour(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Coup de poêle</t>
@@ -807,7 +807,7 @@
     <t xml:space="preserve">Pas chassé</t>
   </si>
   <si>
-    <t xml:space="preserve">Se déplace de [N] cases.</t>
+    <t xml:space="preserve">Se déplace de [N] case(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Goûter</t>
@@ -852,7 +852,7 @@
     <t xml:space="preserve">Réduction</t>
   </si>
   <si>
-    <t xml:space="preserve">Retire [N] points d'armure par réussite.</t>
+    <t xml:space="preserve">Retire [N] point(s) d'armure par réussite.</t>
   </si>
   <si>
     <t xml:space="preserve">Flambage</t>
@@ -870,13 +870,13 @@
     <t xml:space="preserve">Feuilletage</t>
   </si>
   <si>
-    <t xml:space="preserve">Pare [N] coups par tour.</t>
+    <t xml:space="preserve">Pare [N] coup(s) par tour.</t>
   </si>
   <si>
     <t xml:space="preserve">Glaçage</t>
   </si>
   <si>
-    <t xml:space="preserve">Fige la cible pendant [N] tours.</t>
+    <t xml:space="preserve">Fige la cible pendant [N] tour(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Coup de chalumeau</t>
@@ -891,19 +891,19 @@
     <t xml:space="preserve">Style de combat, Passif</t>
   </si>
   <si>
-    <t xml:space="preserve">Seul sur sa case : [N] avantages.</t>
+    <t xml:space="preserve">Seul sur sa case : [N] avantage(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Brigade</t>
   </si>
   <si>
-    <t xml:space="preserve">Avec un allié sur sa case : [N] avantages.</t>
+    <t xml:space="preserve">Avec un allié sur sa case : [N] avantage(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Minutie</t>
   </si>
   <si>
-    <t xml:space="preserve">Contre la même cible : [N] avantages.</t>
+    <t xml:space="preserve">Contre la même cible : [N] avantage(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Maîtrise du lourd</t>
@@ -912,25 +912,25 @@
     <t xml:space="preserve">Maîtrise, Passif</t>
   </si>
   <si>
-    <t xml:space="preserve">Les [N] premières capacités d'un objet Lourde, sans désavantage.</t>
+    <t xml:space="preserve">Sans désavantage pour [N] capacité(s) d'un objet Lourde, en commençant par la première.</t>
   </si>
   <si>
     <t xml:space="preserve">Maîtrise de l'agile</t>
   </si>
   <si>
-    <t xml:space="preserve">Les [N] premières capacités d'un objet Agile, sans désavantage.</t>
+    <t xml:space="preserve">Sans désavantage pour [N] capacité(s) d'un objet Agile, en commençant par la première.</t>
   </si>
   <si>
     <t xml:space="preserve">Maîtrise du précis</t>
   </si>
   <si>
-    <t xml:space="preserve">Les [N] premières capacités d'un objet Précise, sans désavantage.</t>
+    <t xml:space="preserve">Sans désavantage pour [N] capacité(s) d'un objet Précise, en commençant par la première.</t>
   </si>
   <si>
     <t xml:space="preserve">2*N</t>
   </si>
   <si>
-    <t xml:space="preserve">Fait bouillir [N] marmites.</t>
+    <t xml:space="preserve">Fait bouillir [N] marmite(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Une fois par jour, relance un dé.</t>
@@ -954,13 +954,13 @@
     <t xml:space="preserve">Portée[2]</t>
   </si>
   <si>
-    <t xml:space="preserve">Aveugle une cible à {portee} cases.</t>
+    <t xml:space="preserve">Aveugle une cible à {portee} case(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Braise</t>
   </si>
   <si>
-    <t xml:space="preserve">Rallume [N] feux.</t>
+    <t xml:space="preserve">Rallume [N] feu(x).</t>
   </si>
   <si>
     <t xml:space="preserve">Cendre</t>
@@ -987,7 +987,7 @@
     <t xml:space="preserve">Une réussite de plus si vous en avez une.</t>
   </si>
   <si>
-    <t xml:space="preserve">Reportez les dommages sur les {defense} points du couvercle.</t>
+    <t xml:space="preserve">Reportez les dommages sur les {defense} point(s) du couvercle.</t>
   </si>
   <si>
     <t xml:space="preserve">Regagnez 5 points de résistance.</t>
@@ -996,7 +996,7 @@
     <t xml:space="preserve">Pas de côté</t>
   </si>
   <si>
-    <t xml:space="preserve">Annulez [X] dégâts reçus.</t>
+    <t xml:space="preserve">Annulez [X] dégât(s) reçu(s).</t>
   </si>
   <si>
     <t xml:space="preserve">Base : intervention, coût X</t>

--- a/essais/classeur_essai.xlsx
+++ b/essais/classeur_essai.xlsx
@@ -321,7 +321,7 @@
     <t xml:space="preserve">Fournaise, (Braise | Cendre)</t>
   </si>
   <si>
-    <t xml:space="preserve">Primordial : une capacité à trois puissances, un choix</t>
+    <t xml:space="preserve">Chaleur, cuisson, appétit</t>
   </si>
   <si>
     <t xml:space="preserve">Primordial</t>
@@ -330,7 +330,7 @@
     <t xml:space="preserve">Givre éternel</t>
   </si>
   <si>
-    <t xml:space="preserve">Primordial sans capacité ; I3</t>
+    <t xml:space="preserve">Froid, patience, conservation</t>
   </si>
   <si>
     <t xml:space="preserve">Rouleau de fonte</t>

--- a/essais/classeur_essai.xlsx
+++ b/essais/classeur_essai.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="401">
   <si>
     <t xml:space="preserve">Syntaxe</t>
   </si>
@@ -483,6 +483,27 @@
     <t xml:space="preserve">armure naturelle</t>
   </si>
   <si>
+    <t xml:space="preserve">Blessure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Cheville tordue | Main brûlée | Côtes froissées]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloc de blessure : type État, nommé Blessure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">État</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Étourdi | En nage | Affamé]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">États</t>
+  </si>
+  <si>
     <t xml:space="preserve">Paramètres reçus</t>
   </si>
   <si>
@@ -631,6 +652,12 @@
   </si>
   <si>
     <t xml:space="preserve">Agit sans action.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centré</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touche toute la case de son auteur.</t>
   </si>
   <si>
     <t xml:space="preserve">puissance</t>
@@ -1006,6 +1033,42 @@
   </si>
   <si>
     <t xml:space="preserve">Après un déplacement, ou pour finir son tour : une de vos capacités se joue en intervention jusqu'au prochain tour de votre camp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheville tordue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vos déplacements coûtent une action de plus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main brûlée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Désavantage avec une arme précise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Côtes froissées</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vos interventions coûtent 1 souffle de plus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Étourdi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Votre prochaine action coûte une action de plus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En nage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vos jets de défense ont un désavantage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Affamé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vous ne regagnez pas de souffle.</t>
   </si>
   <si>
     <t xml:space="preserve">Forme</t>
@@ -1923,6 +1986,34 @@
         <v>155</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" t="s">
+        <v>157</v>
+      </c>
+      <c r="E40" t="s">
+        <v>158</v>
+      </c>
+      <c r="F40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" t="s">
+        <v>161</v>
+      </c>
+      <c r="E41" t="s">
+        <v>162</v>
+      </c>
+      <c r="F41" t="s">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -1935,10 +2026,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B1" t="s">
-        <x:v>156</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C1" t="s">
-        <x:v>157</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -1946,37 +2037,37 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C2" t="s">
-        <x:v>158</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="s">
-        <x:v>159</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B3" t="s">
-        <x:v>160</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C3" t="s">
-        <x:v>161</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="s">
-        <x:v>162</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B4" t="s">
-        <x:v>163</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C4" t="s">
-        <x:v>164</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="s">
-        <x:v>165</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C5" t="s">
-        <x:v>166</x:v>
+        <x:v>173</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1984,34 +2075,34 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B6" t="s">
-        <x:v>167</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>168</x:v>
+        <x:v>175</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="s">
-        <x:v>169</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>170</x:v>
+        <x:v>177</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="s">
-        <x:v>171</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="B8" t="s">
-        <x:v>172</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="s">
-        <x:v>173</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>174</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -2019,15 +2110,15 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>175</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="B11" t="s">
-        <x:v>176</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>177</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -2035,31 +2126,31 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>178</x:v>
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="s">
-        <x:v>179</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>180</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="s">
-        <x:v>181</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>182</x:v>
+        <x:v>189</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="s">
-        <x:v>183</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>184</x:v>
+        <x:v>191</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -2067,21 +2158,21 @@
         <x:v>125</x:v>
       </x:c>
       <x:c r="B16" t="s">
-        <x:v>185</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C16" t="s">
-        <x:v>186</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="s">
-        <x:v>187</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B17" t="s">
-        <x:v>188</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C17" t="s">
-        <x:v>189</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -2089,64 +2180,72 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B18" t="s">
-        <x:v>190</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C18" t="s">
-        <x:v>191</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="s">
-        <x:v>192</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B19" t="s">
-        <x:v>193</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="C19" t="s">
-        <x:v>194</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="s">
-        <x:v>195</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="B20" t="s">
-        <x:v>196</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C20" t="s">
-        <x:v>197</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="s">
-        <x:v>198</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C21" t="s">
-        <x:v>199</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="s">
-        <x:v>200</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C22" t="s">
-        <x:v>201</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="s">
-        <x:v>202</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C23" t="s">
-        <x:v>203</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="s">
-        <x:v>204</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C24" t="s">
-        <x:v>205</x:v>
+        <x:v>212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C25" t="s">
+        <x:v>214</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2161,22 +2260,22 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C1" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="D1" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="E1" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="F1" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="G1" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2">
@@ -2193,7 +2292,7 @@
         <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="G2" t="s">
         <v>17</v>
@@ -2201,47 +2300,50 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
         <v>213</v>
       </c>
-      <c r="B3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="F3" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="G3" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E4" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="F4" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="G4" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -2250,18 +2352,18 @@
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F5" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="G5" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -2270,15 +2372,15 @@
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B7">
         <v>3</v>
@@ -2290,15 +2392,15 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -2307,74 +2409,74 @@
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F8" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="G8" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="B9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="B10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B12">
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="B13" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C13" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E13" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="F13" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G13" t="s">
         <v>71</v>
@@ -2382,7 +2484,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -2394,80 +2496,80 @@
         <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F15" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="G15" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B16">
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="G16" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="B17">
         <v>0</v>
       </c>
       <c r="G17" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="F18" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="G18" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="B19">
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="G19" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20">
@@ -2478,27 +2580,27 @@
         <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="G20" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B21" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C21" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="G21" t="s">
         <v>80</v>
@@ -2506,13 +2608,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="B22">
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="G22" t="s">
         <v>80</v>
@@ -2520,30 +2622,30 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="B23" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="F23" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="G23" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E24" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F24" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="G24" t="s">
         <v>83</v>
@@ -2551,7 +2653,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2560,10 +2662,10 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F25" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="G25" t="s">
         <v>83</v>
@@ -2571,16 +2673,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B26" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E26" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F26" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="G26" t="s">
         <v>83</v>
@@ -2588,7 +2690,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2597,10 +2699,10 @@
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F27" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="G27" t="s">
         <v>83</v>
@@ -2608,16 +2710,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B28" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E28" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F28" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="G28" t="s">
         <v>89</v>
@@ -2625,16 +2727,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="B29" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C29" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="F29" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="G29" t="s">
         <v>89</v>
@@ -2642,16 +2744,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B30">
         <v>0</v>
       </c>
       <c r="E30" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F30" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="G30" t="s">
         <v>89</v>
@@ -2659,16 +2761,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E31" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="F31" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="G31" t="s">
         <v>89</v>
@@ -2676,16 +2778,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C32" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="F32" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="G32" t="s">
         <v>89</v>
@@ -2693,7 +2795,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2702,10 +2804,10 @@
         <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F33" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="G33" t="s">
         <v>89</v>
@@ -2713,10 +2815,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -2725,21 +2827,21 @@
         <v>0</v>
       </c>
       <c r="E34" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="F34" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="G34" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -2748,21 +2850,21 @@
         <v>0</v>
       </c>
       <c r="E35" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="F35" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="G35" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2771,64 +2873,64 @@
         <v>0</v>
       </c>
       <c r="E36" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="F36" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="G36" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E37" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F37" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="G37" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F38" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G38" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="E39" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="F39" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="G39" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40">
@@ -2836,13 +2938,13 @@
         <v>94</v>
       </c>
       <c r="B40" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="C40" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="F40" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="G40" t="s">
         <v>95</v>
@@ -2856,7 +2958,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="G41" t="s">
         <v>95</v>
@@ -2864,7 +2966,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -2876,15 +2978,15 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="G42" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -2896,15 +2998,15 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="F43" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="B44">
         <v>3</v>
@@ -2916,24 +3018,24 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="F44" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="G45" t="s">
         <v>103</v>
@@ -2941,7 +3043,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -2953,7 +3055,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="G46" t="s">
         <v>103</v>
@@ -2961,13 +3063,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="G47" t="s">
         <v>18</v>
@@ -2975,7 +3077,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -2984,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="G48" t="s">
         <v>18</v>
@@ -2992,7 +3094,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -3001,7 +3103,7 @@
         <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="G49" t="s">
         <v>18</v>
@@ -3015,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="G50" t="s">
         <v>144</v>
@@ -3029,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G51" t="s">
         <v>147</v>
@@ -3037,36 +3139,138 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="B52">
         <v>0</v>
       </c>
       <c r="C52" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="E52" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="F52" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="G52" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="B53">
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="G53" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>336</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="E54" t="s">
+        <v>211</v>
+      </c>
+      <c r="F54" t="s">
+        <v>337</v>
+      </c>
+      <c r="G54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>338</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="E55" t="s">
+        <v>211</v>
+      </c>
+      <c r="F55" t="s">
+        <v>339</v>
+      </c>
+      <c r="G55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>340</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="E56" t="s">
+        <v>211</v>
+      </c>
+      <c r="F56" t="s">
+        <v>341</v>
+      </c>
+      <c r="G56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>342</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="E57" t="s">
+        <v>211</v>
+      </c>
+      <c r="F57" t="s">
+        <v>343</v>
+      </c>
+      <c r="G57" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>344</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="E58" t="s">
+        <v>211</v>
+      </c>
+      <c r="F58" t="s">
+        <v>345</v>
+      </c>
+      <c r="G58" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>346</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="E59" t="s">
+        <v>211</v>
+      </c>
+      <c r="F59" t="s">
+        <v>347</v>
+      </c>
+      <c r="G59" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -3078,23 +3282,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="B1" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="B2" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -3104,39 +3308,39 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="B4" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="B5" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="B6" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="B7" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="B8" t="str">
         <f>CONCATENATE("for","mule")</f>
@@ -3145,7 +3349,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="B9" t="b">
         <v>1</v>
@@ -3156,7 +3360,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="B10" t="e">
         <v>#N/A</v>
@@ -3164,7 +3368,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -3184,10 +3388,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="AB13" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -3202,28 +3406,28 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="C1" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="D1" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="E1" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="F1" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="G1" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="H1" t="s">
         <v>39</v>
       </c>
       <c r="I1" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="J1" t="s">
         <v>11</v>
@@ -3231,13 +3435,13 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="B2" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="C2" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -3252,18 +3456,18 @@
         <v>4</v>
       </c>
       <c r="I2" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="J2" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="B3" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -3275,63 +3479,63 @@
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="I3" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="J3" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="B4" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="J4" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="B5" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="I5" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="J5" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="B6" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="E6" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="H6" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="J6" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="C7" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="D7">
         <v>2</v>
@@ -3346,18 +3550,18 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="J7" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C8" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -3369,10 +3573,10 @@
         <v>3</v>
       </c>
       <c r="I8" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="J8" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
